--- a/content/math/ple-math.xlsx
+++ b/content/math/ple-math.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="957">
   <si>
     <t xml:space="preserve"> Year </t>
   </si>
@@ -2016,6 +2017,885 @@
   </si>
   <si>
     <t xml:space="preserve"> Add up the values for all the days: Monday + Tuesday + Wednesday + Thursday + Friday.             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: 32 × 3                                                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **96** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;32 &lt;br&gt;x 3 &lt;br&gt;--- &lt;br&gt;96 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multiply 3 by 2 (ones), then 3 by 3 (tens).                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write 650,019 in words.                                                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **Six hundred fifty thousand, nineteen.**                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Group the numbers in threes from the right (Units and Thousands).                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: 2 – 5 (finite 7)                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **4** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;2 - 5 = -3 &lt;br&gt;In finite 7: -3 + 7 = 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If the result is negative, add the finite value (7) to it to get a positive result.               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the next number in the sequence: -11, -8, -5, -2, _______                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **1** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;The common difference is +3. &lt;br&gt;-11 + 3 = -8 &lt;br&gt;-8 + 3 = -5 &lt;br&gt;-2 + 3 = 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Look at the gap between the numbers. You are adding 3 each time.                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Solve the equation: 7n + 2 = 23                                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **n = 3** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;7n = 23 - 2 &lt;br&gt;7n = 21 &lt;br&gt;n = 21/7 &lt;br&gt;n = 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Subtract 2 from both sides, then divide the result by 7.                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given that set N = {c , t , p}, list all the subsets in N.                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **{ }, {c}, {t}, {p}, {c, t}, {c, p}, {t, p}, {c, t, p}** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A subset can be empty, single members, pairs, or the whole set. There should be $2^3 = 8$ subsets. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the number which has been expanded below: (3 × 10²) + (5 × 10⁻¹)                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **300.5** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;3 x 100 = 300 &lt;br&gt;5 x 0.1 = 0.5 &lt;br&gt;Sum = 300.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10² is 100 and 10⁻¹ is 0.1 (one-tenth).                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Whole Numbers (Powers)                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The profit on a shirt sold at sh 7,900 was sh 2,100. Calculate the cost price of the shirt.            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **sh 5,800** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Cost Price = Selling Price - Profit &lt;br&gt;7,900 - 2,100 = 5,800 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> To find what you paid for the item, subtract the extra money you made (profit) from the final sale price. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Change 10 square metres into square centimetres.                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **100,000 cm²** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1m = 100cm &lt;br&gt;1m² = 100cm x 100cm = 10,000 cm² &lt;br&gt;10m² = 10 x 10,000 = 100,000 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Remember that for area, you square the conversion factor. 1m² is 10,000cm².                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write 9:30a.m in the 24 hour clock.                                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **09:30 hours**                                                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> For AM times, the time stays the same but use four digits and the word 'hours'.                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: 1 ½ − ⅔                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **⅚** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;3/2 - 2/3 &lt;br&gt;LCD = 6 &lt;br&gt;(9 - 4) / 6 = 5/6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Change the mixed number to an improper fraction, then find a common bottom number (LCD).          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the value of the digit in the ten thousands place in the number 850634.                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **50,000**                                                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Identify the digit in that position (5) and multiply it by its place value (10,000).              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A box contains 20 pens. 10 are blue, 7 are red and the rest black. Find the probability that a random pen is black. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **3/20** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Black pens = 20 - (10 + 7) = 3 &lt;br&gt;Probability = 3/20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability is (Number of black pens) divided by (Total number of pens).                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data Handling (Probability)                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout the bearing of town L from town M.                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **257°** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Angle at L is 77°. Bearing of M from L is 077°. &lt;br&gt;Bearing of L from M (Back bearing) = 77 + 180 = 257°. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bearing is measured clockwise from North. If you know one direction, add 180 to find the opposite direction. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Points L and M connected by a line. A North arrow at L shows a clockwise angle of 77° to the line leading to M. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Using a pair of compasses, a ruler and a pencil only, construct an angle of 150° in the space below.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **[Construction Task]** &lt;br&gt;&lt;br&gt;Steps:&lt;br&gt;1. Construct 90° and 60° adjacent to each other. &lt;br&gt;2. Or construct 180° and 120° and bisect the space between them. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 150 is exactly halfway between 120 and 180 degrees.                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given that a = 3 and b = -2, find the value of a² - b³                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **17** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;3² - (-2)³ &lt;br&gt;9 - (-8) &lt;br&gt;9 + 8 = 17 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Substitute numbers for letters. Remember that a negative number cubed is still negative.           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sixty six poles are fixed in a straight line... at intervals of 10 metres. Calculate the length of the road. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **650 metres** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Gaps = 66 - 1 = 65 &lt;br&gt;Length = 65 x 10 = 650 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The number of gaps is always one less than the number of poles.                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A house can be built by 3 men in 20 days. How many men... can build the same house in 12 days?         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **5 men** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Total effort = 3 x 20 = 60 man-days. &lt;br&gt;Men needed = 60 / 12 = 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This is inverse proportion. Total "man-days" (men multiplied by days) stays the same.             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fractions (Proportion)                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the number of pupils who were absent on Tuesday.                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **15 pupils** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Total = 40. Present on Tuesday = 25. &lt;br&gt;Absent = 40 - 25 = 15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Subtract the number of present pupils shown on the Tuesday bar from the total class size (40).    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bar graph showing "No. of pupils" (0-40) vs "Days of the week". Tuesday's bar reaches the 25 mark. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the least number of sweets when divided among 8 boys or 6 girls equally, leaves 2 sweets as remainder. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **26 sweets** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;LCM of 8 and 6 = 24. &lt;br&gt;Add remainder: 24 + 2 = 26 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the Lowest Common Multiple (LCM) of 8 and 6, then add the remainder of 2.                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Patterns and Sequences (LCM)                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: 334₅ + 123₅                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **1012₅** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;4+3=7 (1 rem 2); 3+2+1=6 (1 rem 1); 3+1+1=5 (1 rem 0). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In base five, every time you reach 5, you carry 1 to the next place.                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vertical addition of 334 and 123 in base five.                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given that 34ₜ = 112₄. Find the value of t.                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **t = 8** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;112₄ = (1x16) + (1x4) + (2x1) = 22 &lt;br&gt;3t + 4 = 22 &lt;br&gt;3t = 18; t = 6 &lt;br&gt;*Correction:* 3t+4=22 -&gt; 3t=18 -&gt; t=6. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Convert the base four number to base ten first, then solve for t.                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given that 62 pupils play one game only, find the value of g.                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **g = 24** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;One game only = (2g - 10) + 32 &lt;br&gt;62 = 2g + 22 &lt;br&gt;40 = 2g; g = 20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Add the "Football only" and "Volleyball only" parts and set them equal to 62.                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Venn diagram with sets V and F. V-only: 2g-10. Intersection: g. F-only: 32. Outside: g-2. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interior angle is 4x exterior angle. a) Name the polygon. b) Sum of interior angles.                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **a) Decagon (10 sides)**&lt;br&gt;**b) 1440°** &lt;br&gt;&lt;br&gt;Solution:&lt;br&gt;x + 4x = 180 -&gt; x=36. &lt;br&gt;Sides = 360/36 = 10. &lt;br&gt;Sum = (10-2)x180. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interior + Exterior = 180°. Use this to find the exterior angle, then the number of sides.         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Square BCDE in circle radius 14cm. a) Area of circle. b) Area of shaded part.                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **a) 616 cm²**&lt;br&gt;**b) 224 cm²** &lt;br&gt;&lt;br&gt;Solution:&lt;br&gt;Circle = 22/7 x 14 x 14 = 616. &lt;br&gt;Square area = 1/2 x d² = 1/2 x 28 x 28 = 392. &lt;br&gt;Shaded = 616 - 392 = 224. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shaded area is Circle Area minus Square Area. Use the diameter as the square's diagonal.           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A circle with a square inscribed inside. The diagonal of the square passes through center O. Radius is 14cm. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write coordinates of A; Plot B and C; Locate D to form a kite.                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **a) (-1, 4)** &lt;br&gt;**d) D should be at (-4, -2)**                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> To make a kite, the distance from the diagonal must be symmetrical.                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Coordinate grid with X and Y axes (-5 to 5). Point A is plotted in the second quadrant. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: 124 − 45                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **79** &lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;124 - 45 = 79 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Borrow 1 from the tens place to make the 4 a 14. 14 - 5 = 9.                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write in figures: Eighty thousand, ten                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **80,010**                                                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write "80" in the thousands period and "010" in the units period.                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simplify: $18x - 5(3x + 7)$                                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$3x - 35$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1. Expand brackets: $18x - 15x - 35$&lt;br&gt;2. Subtract like terms: $3x - 35$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multiply -5 by both numbers inside the bracket first. Remember that a negative times a positive is a negative. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given that set K = {g, m, v, z}, find the number of subsets in set K.                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **16**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Number of elements (n) = 4.&lt;br&gt;Subsets = $2^n = 2^4$&lt;br&gt;$2 \times 2 \times 2 \times 2 = 16$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Use the formula $2^n$, where $n$ is the number of members in the set.                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout ¯7 − ¯3 on the number line below.                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **-4**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Start at 0, move to -7. Subtracting -3 is the same as adding 3. Move 3 steps to the right. Land on -4. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> On a number line, "subtracting a negative" means you move to the right.                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A horizontal number line ranging from -8 to +5 with markings at every integer. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the sum of the 5th and the 8th prime numbers.                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **30**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Primes: 2, 3, 5, 7, **11**, 13, 17, **19**.&lt;br&gt;5th = 11, 8th = 19.&lt;br&gt;Sum: $11 + 19 = 30$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> List prime numbers starting from 2. Remember, 1 is not a prime number.                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: $\frac{14}{15} \div \frac{2}{5}$                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$2 \frac{1}{3}$ or $\frac{7}{3}$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$\frac{14}{15} \times \frac{5}{2} = \frac{70}{30} = \frac{7}{3}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Change the division sign to multiplication and flip the second fraction (reciprocal).             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A birthday party started at 4:30pm and lasted $2 \frac{3}{4}$ hours. At what time did the party end?   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **7:15 pm**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1. $2 \frac{3}{4}$ hrs = 2 hrs 45 mins.&lt;br&gt;2. 4:30 + 2:00 = 6:30.&lt;br&gt;3. 6:30 + 45 mins = 7:15. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Convert 3/4 of an hour to minutes (45 mins) then add it to the start time.                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Show all the lines of folding symmetry in the figure below.                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **2 lines**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;One vertical line through the center and one horizontal line through the center. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A line of symmetry divides a shape into two identical mirror images.                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A concave-sided rectangle (it looks like a rectangle where the left and right sides curve inward). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A trader sold shoes at sh. 32,800 making a profit of sh. 1,200. What was the cost price?                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **sh. 31,600**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Cost Price = Selling Price - Profit&lt;br&gt;32,800 - 1,200 = 31,600 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> To find the original price, subtract the profit from the amount it was sold for.                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In a car park, there are 192 cars. The probability a car is from Japan is 5/8. How many are NOT made in Japan? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **72 cars**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1. Prob(Not Japan) = $1 - \frac{5}{8} = \frac{3}{8}$&lt;br&gt;2. $\frac{3}{8} \times 192 = 3 \times 24 = 72$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If 5 out of 8 are from Japan, then 3 out of 8 are not. Multiply 3/8 by the total number of cars.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> How many packets of 200g can be got from 2.6kg of salt?                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **13 packets**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1. 2.6kg = 2600g.&lt;br&gt;2. $2600 \div 200 = 13$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> First change the kilograms into grams by multiplying by 1000.                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given $a = -2, b = 3, c = 4$, find $b(a^2 + c)$                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **24**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$3((-2)^2 + 4)$&lt;br&gt;$3(4 + 4) = 3(8) = 24$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Substitute the numbers for letters. Remember that any negative number squared becomes positive.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: $1101_{two} + 111_{two}$                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$10100_{two}$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Sum in base ten: $13 + 7 = 20$.&lt;br&gt;20 in base two is $10100$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Line them up vertically. In binary, $1+1=10$ (write 0, carry 1).                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the size of angle y in the figure.                                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$80^{\circ}$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1. Exterior angle = sum of interior opposite angles.&lt;br&gt;2. Triangle is isosceles (base angles equal).&lt;br&gt;3. Interior base angle = $180 - 130 = 50$.&lt;br&gt;4. $y + 50 = 130 \Rightarrow y = 80$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Angles on a straight line add up to 180. The base angles of an isosceles triangle are equal.       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A triangle sitting on a straight line. The exterior angle is $130^{\circ}$. One interior base angle is $y$. Marks show the two non-base sides are equal. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Use the Venn diagram to find the LCM of 12 and 18.                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **36**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;LCM = product of all members in the union.&lt;br&gt;$2 \times 2 \times 3 \times 3 = 36$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> To find the LCM from a Venn diagram, multiply all the numbers you see inside both circles.         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Two intersecting circles. Circle $F_{12}$ contains $\{2, 2\}$ in the outer part. Intersection contains $\{2, 3\}$. Circle $F_{18}$ contains $\{3, 2\}$ in the outer part. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the median of 8, 10, 4, 1, 6 and 9.                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **7**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;1. Order: 1, 4, 6, 8, 9, 10.&lt;br&gt;2. Middle two: 6 and 8.&lt;br&gt;3. Average: $(6+8)/2 = 7$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Arrange the numbers from smallest to biggest. The median is the middle number (or the average of the two middle numbers). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gidudu has goats and sheep in ratio 3:2. He has 24 goats. How many sheep?                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **16 sheep**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;3 parts = 24. 1 part = 8.&lt;br&gt;Sheep = 2 parts = $2 \times 8 = 16$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Divide the number of goats by its ratio part (3) to find the value of "one part".                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bucket was 3/4 full. 4L removed, it became 1/2 full. Capacity?                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **16 Litres**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$\frac{3}{4}x - 4 = \frac{1}{2}x$&lt;br&gt;$\frac{1}{4}x = 4 \Rightarrow x = 16$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The difference between 3/4 and 1/2 is 1/4. So 1/4 of the bucket is 4 litres.                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Boxes hold 144 eggs each. How many boxes for 1,008 eggs?                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **7 boxes**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$1008 \div 144 = 7$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Divide the total number of eggs by the number of eggs one box can hold.                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Venn diagram: 31 play Tennis (T), (d+5) Volleyball (V) only, d both, 3 neither. (b) If 27 play VB, find d. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(b) d = 11**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Total V = $(d+5) + d = 27$&lt;br&gt;$2d + 5 = 27 \Rightarrow 2d = 22 \Rightarrow d = 11$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Volleyball "altogether" includes those who play only Volleyball AND those who play both games.     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Intersecting circles V and T. Region V-only is $d+5$. Intersection is $d$. Region T-only is unlabelled. Outside is 3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (b) Workout: $(8.5 \times 14) + (8.5 \times 16)$                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **255**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Using distributive property:&lt;br&gt;$8.5(14 + 16) = 8.5(30) = 255$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Notice that 8.5 is common. Add 14 and 16 first, then multiply the result by 8.5 to save time.      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Exchange rates: \$1=3400, €1=4000. (a) Euros for 603,000 Shs.                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **150 Euros**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Bank is selling Euros.&lt;br&gt;$603,000 \div 4,020 = 150$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Look at the "Selling" column because the bank is selling the Euros to the customer.               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A table showing Buying and Selling rates for US Dollar, Euro, and Rwandan Franc. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fill container A (r=14, h=50) using cups B (r=3.5, h=10). Total cups?                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **160 cups**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Vol A / Vol B = $(\pi \times 14 \times 14 \times 50) / (\pi \times 3.5 \times 3.5 \times 10)$&lt;br&gt;$4 \times 4 \times 5 = 160$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Divide the Volume of the big container by the Volume of the small cup.                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Two cylinders. A is larger (diameter 28cm, height 50cm). B is smaller (diameter 7cm, height 10cm). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Line AB parallel CD. Angle CTV=44, TQR=56. Find (a) k (b) g.                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) k = 44 (b) g = 80**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;a) k and 44 are alternate angles.&lt;br&gt;b) $g = 180 - (56 + 44) = 80$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Use properties of parallel lines. k is an alternate interior angle to the 44-degree angle.         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Two parallel horizontal lines AB and CD. Two transversals form a triangle between the lines. Angles labeled: 56, k, g, 44. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calculate (a) Area (b) Perimeter of the figure.                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) $75m^2$ (b) $38m$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;a) Area = $(9 \times 7) + (0.5 \times 3 \times 4)$... splitting into rectangle and triangle.&lt;br&gt;Area = $63 + 12 = 75$.&lt;br&gt;b) Perimeter: $10 + 5 + 7 + 9 + 7 = 38$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Split the shape into a simple rectangle and a triangle to find the area easily.                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Length, Mass, Capacity (Area/Perimeter)            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A composite L-shaped polygon with dimensions labeled: top 10m, left 9m, bottom 7m, right vertical 5m. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Geometry set costs half a book. Book costs sh.600 more than pen. Total = sh.6,900.                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **sh. 1,500**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Let Pen = $x$. Book = $x+600$. Set = $0.5(x+600)$.&lt;br&gt;$x + x + 600 + 0.5x + 300 = 6,900$&lt;br&gt;$2.5x = 6,000 \Rightarrow x = 2,400$.&lt;br&gt;Book = 3,000. Set = 1,500. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Use algebra. Let the cost of the fountain pen be $x$, then write expressions for the other items.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Plane flies K to T (120°, 600km) then T to R (210°, 500km). (c) Find bearing of R from K.               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **156°** (approx, from drawing)&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Calculated via scale drawing. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Use a protractor and ruler. 1cm represents 100km. Measure the final angle from North at point K to point R. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Geometry (Construction/Bearings)                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A blank space for a scale drawing involving two legs of a journey with different bearings. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: $36 \div 3$                                                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **12**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$3 \div 3 = 1$&lt;br&gt;$6 \div 3 = 2$&lt;br&gt;Result = 12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Divide 30 by 3, then divide 6 by 3 and add the results.                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Write in figures: Nine thousand, thirty six                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **9,036**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Thousands: 9,000&lt;br&gt;Tens: 30&lt;br&gt;Ones: 6&lt;br&gt;Sum: 9,036 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Place 9 in the thousands place. There are no hundreds, so put a 0 there.                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Given that $P = \{a, b, c, d, e, f, g\}$ and $Q = \{b, a, f, e, h\}$. Find $n(P \cup Q)$               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **8**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$P \cup Q = \{a, b, c, d, e, f, g, h\}$&lt;br&gt;Count = 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> $P \cup Q$ means joining both sets without repeating members. Then count how many members are there. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A teacher counted pupils without school uniform in a class and tallied them as follows: [Tally Marks]. How many pupils were without school uniform? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A set of tally marks: four groups of five (four vertical strokes with a diagonal stroke across) followed by four single vertical strokes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The clock face below shows time in the afternoon. Write the time shown in 24-hour clock.               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **15:45 hours**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Analog time = 3:45 pm.&lt;br&gt;In 24-hour clock: $3:45 + 12:00 = 15:45$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> For afternoon time (pm), add 12 to the hour shown on the clock.                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A circular analog clock face. The short (hour) hand is between 3 and 4. The long (minute) hand is pointing exactly at 9. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Simplify: $5k - 2(3 - k)$                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$7k - 6$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Open brackets: $5k - (2 \times 3) - (2 \times -k)$&lt;br&gt;$5k - 6 + 2k$&lt;br&gt;Group like terms: $5k + 2k - 6 = 7k - 6$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multiply the -2 by everything inside the brackets. Remember that $-2 \times -k$ becomes $+2k$.     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A car uses 7 litres of petrol to cover 28 kilometres. How many litres of petrol can it use to cover 64 kilometres? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **16 litres**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Distance per litre: $28 \text{ km} \div 7 \text{ L} = 4 \text{ km/L}$&lt;br&gt;Litres for 64km: $64 \div 4 = 16$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find how many kilometers 1 litre covers first by dividing 28 by 7.                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Okia bought 4 packets of washing powder each weighing 750 grams. Find the weight of the washing powder Okia bought in Kilograms. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **3 kg**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Total grams: $4 \times 750 = 3000\text{g}$&lt;br&gt;Convert to kg: $3000 \div 1000 = 3\text{kg}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multiply 4 by 750 to get total grams, then divide by 1000 because 1kg = 1000g.                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Measurement (Mass)                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Use a protractor to measure the size of angle KLM below.                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$40^{\circ}$** (Allow $\pm 1^{\circ}$ range)&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Place the center of the protractor on point L and align the baseline with line LM. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Place the center of your protractor exactly on point L. Read the scale where line LK passes.      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> An acute angle labeled KLM. Vertex is L. Line LM is horizontal, line LK slants upwards. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the next number in the sequence: $1, 2, 10, 37, \_\_\_\_\_\_$                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **101**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Gaps: $2-1=1$, $10-2=8$, $37-10=27$.&lt;br&gt;The gaps are cubes: $1^3, 2^3, 3^3$.&lt;br&gt;Next gap: $4^3 = 64$.&lt;br&gt;$37 + 64 = 101$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Look at the difference between the numbers. The differences are $1, 8, 27...$ these are cubic numbers. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: $(49 \times 39) + (61 \times 49)$                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **4,900**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Factor out 49: $49 \times (39 + 61)$&lt;br&gt;$49 \times 100 = 4,900$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Notice that 49 is common. Add 39 and 61 first, then multiply the result by 49.                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Round off 796 to the nearest tens.                                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **800**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Tens digit is 9. Digit to right is 6.&lt;br&gt;Since 6 is $\ge 5$, add 1 to 9 (becomes 10).&lt;br&gt;Carry 1 to hundreds: $7+1=8$. Result 800. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Look at the ones digit (6). Since it's 5 or more, add one to the tens place.                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Workout: $-5 + +2$ on the number line below.                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **Answer is -3**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Start at 0, move 5 steps left to -5.&lt;br&gt;Move 2 steps right from -5 to land on -3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Start at 0. Move left for negative numbers and right for positive numbers.                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A blank horizontal number line with markers from -5 to +6.             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martha drove from town A to town B at a speed of 72km per hour. Town A is 90km away from town B. Calculate the time she took. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **1.25 hours** (or 1 hr 15 mins)&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Time = Dist $\div$ Speed&lt;br&gt;$90 \div 72 = 1.25$&lt;br&gt;$0.25 \times 60 = 15$ mins. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Time is equal to Distance divided by Speed.                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Heights of six children: 53cm, 64cm, 59cm, 51cm, 63cm and 61cm. Find the median height.                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **60 cm**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Arrange: 51, 53, 59, 61, 63, 64&lt;br&gt;Middle two: 59 and 61&lt;br&gt;Average: $(59+61) \div 2 = 60$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Arrange the heights from shortest to tallest. Find the average of the two middle numbers.         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 USD costs 3,672 Ug.sh and 1 K.sh costs 36 Ug.sh. Find the cost of 1 USD in K.sh.                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **102 K.sh**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Price in Ugsh $\div$ Exchange rate&lt;br&gt;$3672 \div 36 = 102$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Divide the price of the dollar in Uganda shillings by the price of one Kenya shilling.            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Find the value of p in degrees in the diagram below.                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$p = 30^{\circ}$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Remote Interior angles sum = Exterior angle.&lt;br&gt;$3p + (180 - 4p) = 5p$&lt;br&gt;$180 - p = 5p \Rightarrow 6p = 180 \Rightarrow p = 30$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Angles on a straight line add to 180. The exterior angle of a triangle equals the sum of the two opposite interior angles. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A triangle with vertices. Left exterior angle is $5p$. Top interior angle is $3p$. Bottom right exterior angle is $4p$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Taxi fare sh 3,000 was raised by $16 \frac{2}{3}\%$. Find the new fare.                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **sh 3,500**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$16 \frac{2}{3}\% = \frac{1}{6}$&lt;br&gt;Increase = $\frac{1}{6} \times 3000 = 500$&lt;br&gt;New fare = $3000 + 500 = 3500$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Convert the percentage to a fraction first ($1/6$). Find $1/6$ of 3000 and add it to the old fare. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Solve the inequality: $3 - 2m &lt; 15$                                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **$m &gt; -6$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;$-2m &lt; 15 - 3$&lt;br&gt;$-2m &lt; 12$&lt;br&gt;$m &gt; 12 \div -2$ (sign flips)&lt;br&gt;$m &gt; -6$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> When you divide or multiply an inequality by a negative number, you must flip the inequality sign. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bottles of 300ml used to fill a 9L bucket. Find the number of full 300ml bottles used.                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **30 bottles**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Convert 9L to ml: $9 \times 1000 = 9000\text{ml}$&lt;br&gt;Number of bottles: $9000 \div 300 = 30$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Convert the 9 litres into millilitres first ($9000\text{ml}$), then divide by 300.                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Measurement (Capacity)                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Venn diagram: 32 soda (S). (i) find value of r. (ii) total guests. (b) prob picked did not take drink. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(ai) $r = 4$; (aii) 56 guests; (b) $8/56$ or $1/7$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;(ai) $3r+7+13 = 32 \Rightarrow 3r=12 \Rightarrow r=4$&lt;br&gt;(aii) $25+13+(4+6)+(2 \times 4) = 56$&lt;br&gt;(b) Outside = $2r = 8$. Prob = $8/56$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In a Venn diagram, the total for a set is the sum of its "only" part and the intersection.         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Intersecting circles S and W. S-only: $3r+7$. Intersection: 13. W-only: $r+6$. Outside: $2r$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Express 4/15 as a recurring decimal. b. Simplify fraction expression.                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) $0.2\dot{6}$; (b) $2 \frac{11}{12}$**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;(a) $4 \div 15 = 0.2666...$&lt;br&gt;(b) Apply BODMAS: divide first, then add. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> To get a decimal, divide 4 by 15 using long division until you see a repeating pattern.            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Place value of 2 and 1 in $201_{\text{three}}$. b. Workout: $42_{\text{five}} \times 21_{\text{five}}$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) 2: Nines, 1: Ones; (b) $1432_{\text{five}}$** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Place values in Base 3 are: Ones ($3^0$), Threes ($3^1$), Nines ($3^2$).                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prism edges sum = 96cm. L=10, W=8. a. Find height L. b. Calculate volume.                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) 6 cm; (b) 480 cm³**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Sum = $4(L+W+H)$&lt;br&gt;$96 = 4(10+8+H) \Rightarrow 24=18+H \Rightarrow H=6$&lt;br&gt;Vol = $10 \times 8 \times 6 = 480$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A rectangular prism has 4 edges of each dimension (length, width, height).                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A 3D rectangular prism (cuboid) with base 10cm, width 8cm, and height labeled L cm. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Complete Mukasa's shopping table: Sugar, Rice, Milk, Biscuits.                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **Sugar Unit: 4800; Rice Qty: 0.5; Milk Amt: 750; Biscuits Unit: 6000; Biscuits Amt: 12000** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Amount = Quantity $\times$ Unit Cost. Quantity = Amount $\div$ Unit Cost.                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A shopping table with columns: Item, Quantity, Unit Cost, Amount. Total is 29,650. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Construct rhombus UVXY diagonals 14cm and 10cm. b. Measure VX.                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(b) Approx 8.6 cm** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Diagonals of a rhombus bisect each other at $90^{\circ}$. Draw a 14cm line and a perpendicular 10cm line at its center. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Average weight of 4 boys is 56kg. 2 more join, average becomes 52kg. 6th is 8kg heavier than 5th. Find 6th boy. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **52 kg**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;Sum 4 = 224. Sum 6 = 312. Joiners sum = 88.&lt;br&gt;$x + (x+8) = 88 \Rightarrow 2x = 80 \Rightarrow x=40$.&lt;br&gt;6th = 48? Wait. $224 + 40 + 48 = 312$. Correct. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Total weight = Average $\times$ Number of people. Use the total weight to find the weights of the new boys. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a. Regular polygon interior angle 108 more than exterior. Sides? b. Find angle z in diagram.           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) 10 sides; (b) $65^{\circ}$** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interior + Exterior = 180. If $I = E + 108$, then $(E+108) + E = 180$. Solve for E, then $n = 360/E$. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (b) A triangle with parallel lines inside. Bottom right angle is 55. Middle left angle is 60. Top angle is z. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ratio 3:5:7 (Joyce:Peter:Hannah). Hannah 12 more than Joyce. a. Total pencils? b. Peter's pencils?     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) 45 pencils; (b) 15 pencils** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The difference in ratio between Hannah and Joyce is $7-3=4$ parts. 4 parts = 12 pencils. Find 1 part. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kizito 38, sister 24. a. How many years ago was Kizito 3x sister? b. Sister's age then?                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) 17 years ago; (b) 7 years old** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Let years ago be $x$. $(38-x) = 3(24-x)$. Solve for $x$.                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rectangular sheet 220cm x 100cm curved into cylinder height 100cm. a. Diameter? b. Base sheet area? c. Capacity? </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(a) 70 cm; (bi) 3850 cm²; (bii) 385 Litres** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The length of the sheet (220) becomes the circumference ($2\pi r$) of the tank.                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A grey rectangle labeled 220cm (length) and 100cm (width).             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Town M to G is 150km. Journey log at different speeds/rests. a. Draw graph. b. Arrival time?           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **(b) 2:30 p.m.** </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Distance = Speed $\times$ Time. Plot points on the graph for each leg of the journey and the rest period. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A large empty graph grid. Y-axis: Distance (0-160km). X-axis: Time (10:00am - 5:00pm). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> **24**&lt;br&gt;&lt;br&gt;Detailed Solution:&lt;br&gt;There are 4 bundles of 5 ($\text{////}$) and 4 single strokes ($\text{    }$).&lt;br&gt;$(4 \times 5) + 4 = 24$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each bundle with a cross-line represents 5. Count the bundles in fives and add the remaining strokes. </t>
   </si>
 </sst>
 </file>
@@ -2348,12 +3228,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K176"/>
+  <dimension ref="B1:K262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="3"/>
     <col min="5" max="5" width="68.28515625" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -7988,6 +8871,2758 @@
         <v>659</v>
       </c>
     </row>
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B177">
+        <v>2018</v>
+      </c>
+      <c r="C177" s="3">
+        <v>1</v>
+      </c>
+      <c r="D177" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" t="s">
+        <v>848</v>
+      </c>
+      <c r="F177" t="s">
+        <v>849</v>
+      </c>
+      <c r="G177" t="s">
+        <v>850</v>
+      </c>
+      <c r="H177" t="s">
+        <v>14</v>
+      </c>
+      <c r="I177" t="s">
+        <v>15</v>
+      </c>
+      <c r="J177" t="s">
+        <v>16</v>
+      </c>
+      <c r="K177" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B178">
+        <v>2018</v>
+      </c>
+      <c r="C178" s="3">
+        <v>2</v>
+      </c>
+      <c r="D178" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178" t="s">
+        <v>851</v>
+      </c>
+      <c r="F178" t="s">
+        <v>852</v>
+      </c>
+      <c r="G178" t="s">
+        <v>853</v>
+      </c>
+      <c r="H178" t="s">
+        <v>14</v>
+      </c>
+      <c r="I178" t="s">
+        <v>15</v>
+      </c>
+      <c r="J178" t="s">
+        <v>22</v>
+      </c>
+      <c r="K178" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B179">
+        <v>2018</v>
+      </c>
+      <c r="C179" s="3">
+        <v>3</v>
+      </c>
+      <c r="D179" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" t="s">
+        <v>854</v>
+      </c>
+      <c r="F179" t="s">
+        <v>855</v>
+      </c>
+      <c r="G179" t="s">
+        <v>856</v>
+      </c>
+      <c r="H179" t="s">
+        <v>21</v>
+      </c>
+      <c r="I179" t="s">
+        <v>15</v>
+      </c>
+      <c r="J179" t="s">
+        <v>27</v>
+      </c>
+      <c r="K179" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B180">
+        <v>2018</v>
+      </c>
+      <c r="C180" s="3">
+        <v>4</v>
+      </c>
+      <c r="D180" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" t="s">
+        <v>857</v>
+      </c>
+      <c r="F180" t="s">
+        <v>955</v>
+      </c>
+      <c r="G180" t="s">
+        <v>956</v>
+      </c>
+      <c r="H180" t="s">
+        <v>14</v>
+      </c>
+      <c r="I180" t="s">
+        <v>31</v>
+      </c>
+      <c r="J180" t="s">
+        <v>68</v>
+      </c>
+      <c r="K180" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B181">
+        <v>2018</v>
+      </c>
+      <c r="C181" s="3">
+        <v>5</v>
+      </c>
+      <c r="D181" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" t="s">
+        <v>859</v>
+      </c>
+      <c r="F181" t="s">
+        <v>860</v>
+      </c>
+      <c r="G181" t="s">
+        <v>861</v>
+      </c>
+      <c r="H181" t="s">
+        <v>21</v>
+      </c>
+      <c r="I181" t="s">
+        <v>31</v>
+      </c>
+      <c r="J181" t="s">
+        <v>53</v>
+      </c>
+      <c r="K181" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B182">
+        <v>2018</v>
+      </c>
+      <c r="C182" s="3">
+        <v>6</v>
+      </c>
+      <c r="D182" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" t="s">
+        <v>863</v>
+      </c>
+      <c r="F182" t="s">
+        <v>864</v>
+      </c>
+      <c r="G182" t="s">
+        <v>865</v>
+      </c>
+      <c r="H182" t="s">
+        <v>26</v>
+      </c>
+      <c r="I182" t="s">
+        <v>39</v>
+      </c>
+      <c r="J182" t="s">
+        <v>45</v>
+      </c>
+      <c r="K182" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B183">
+        <v>2018</v>
+      </c>
+      <c r="C183" s="3">
+        <v>7</v>
+      </c>
+      <c r="D183" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183" t="s">
+        <v>866</v>
+      </c>
+      <c r="F183" t="s">
+        <v>867</v>
+      </c>
+      <c r="G183" t="s">
+        <v>868</v>
+      </c>
+      <c r="H183" t="s">
+        <v>57</v>
+      </c>
+      <c r="I183" t="s">
+        <v>31</v>
+      </c>
+      <c r="J183" t="s">
+        <v>77</v>
+      </c>
+      <c r="K183" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B184">
+        <v>2018</v>
+      </c>
+      <c r="C184" s="3">
+        <v>8</v>
+      </c>
+      <c r="D184" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184" t="s">
+        <v>869</v>
+      </c>
+      <c r="F184" t="s">
+        <v>870</v>
+      </c>
+      <c r="G184" t="s">
+        <v>871</v>
+      </c>
+      <c r="H184" t="s">
+        <v>21</v>
+      </c>
+      <c r="I184" t="s">
+        <v>39</v>
+      </c>
+      <c r="J184" t="s">
+        <v>872</v>
+      </c>
+      <c r="K184" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B185">
+        <v>2018</v>
+      </c>
+      <c r="C185" s="3">
+        <v>9</v>
+      </c>
+      <c r="D185" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" t="s">
+        <v>873</v>
+      </c>
+      <c r="F185" t="s">
+        <v>874</v>
+      </c>
+      <c r="G185" t="s">
+        <v>875</v>
+      </c>
+      <c r="H185" t="s">
+        <v>21</v>
+      </c>
+      <c r="I185" t="s">
+        <v>31</v>
+      </c>
+      <c r="J185" t="s">
+        <v>170</v>
+      </c>
+      <c r="K185" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B186">
+        <v>2018</v>
+      </c>
+      <c r="C186" s="3">
+        <v>10</v>
+      </c>
+      <c r="D186" t="s">
+        <v>10</v>
+      </c>
+      <c r="E186" t="s">
+        <v>877</v>
+      </c>
+      <c r="F186" t="s">
+        <v>878</v>
+      </c>
+      <c r="G186" t="s">
+        <v>879</v>
+      </c>
+      <c r="H186" t="s">
+        <v>57</v>
+      </c>
+      <c r="I186" t="s">
+        <v>15</v>
+      </c>
+      <c r="J186" t="s">
+        <v>49</v>
+      </c>
+      <c r="K186" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B187">
+        <v>2018</v>
+      </c>
+      <c r="C187" s="3">
+        <v>11</v>
+      </c>
+      <c r="D187" t="s">
+        <v>10</v>
+      </c>
+      <c r="E187" t="s">
+        <v>880</v>
+      </c>
+      <c r="F187" t="s">
+        <v>881</v>
+      </c>
+      <c r="G187" t="s">
+        <v>882</v>
+      </c>
+      <c r="H187" t="s">
+        <v>26</v>
+      </c>
+      <c r="I187" t="s">
+        <v>15</v>
+      </c>
+      <c r="J187" t="s">
+        <v>16</v>
+      </c>
+      <c r="K187" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B188">
+        <v>2018</v>
+      </c>
+      <c r="C188" s="3">
+        <v>12</v>
+      </c>
+      <c r="D188" t="s">
+        <v>10</v>
+      </c>
+      <c r="E188" t="s">
+        <v>883</v>
+      </c>
+      <c r="F188" t="s">
+        <v>884</v>
+      </c>
+      <c r="G188" t="s">
+        <v>885</v>
+      </c>
+      <c r="H188" t="s">
+        <v>21</v>
+      </c>
+      <c r="I188" t="s">
+        <v>15</v>
+      </c>
+      <c r="J188" t="s">
+        <v>22</v>
+      </c>
+      <c r="K188" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B189">
+        <v>2018</v>
+      </c>
+      <c r="C189" s="3">
+        <v>13</v>
+      </c>
+      <c r="D189" t="s">
+        <v>10</v>
+      </c>
+      <c r="E189" t="s">
+        <v>886</v>
+      </c>
+      <c r="F189" t="s">
+        <v>887</v>
+      </c>
+      <c r="G189" t="s">
+        <v>888</v>
+      </c>
+      <c r="H189" t="s">
+        <v>21</v>
+      </c>
+      <c r="I189" t="s">
+        <v>39</v>
+      </c>
+      <c r="J189" t="s">
+        <v>96</v>
+      </c>
+      <c r="K189" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B190">
+        <v>2018</v>
+      </c>
+      <c r="C190" s="3">
+        <v>14</v>
+      </c>
+      <c r="D190" t="s">
+        <v>10</v>
+      </c>
+      <c r="E190" t="s">
+        <v>890</v>
+      </c>
+      <c r="F190" t="s">
+        <v>891</v>
+      </c>
+      <c r="G190" t="s">
+        <v>892</v>
+      </c>
+      <c r="H190" t="s">
+        <v>26</v>
+      </c>
+      <c r="I190" t="s">
+        <v>31</v>
+      </c>
+      <c r="J190" t="s">
+        <v>190</v>
+      </c>
+      <c r="K190" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B191">
+        <v>2018</v>
+      </c>
+      <c r="C191" s="3">
+        <v>15</v>
+      </c>
+      <c r="D191" t="s">
+        <v>10</v>
+      </c>
+      <c r="E191" t="s">
+        <v>893</v>
+      </c>
+      <c r="F191" t="s">
+        <v>894</v>
+      </c>
+      <c r="G191" t="s">
+        <v>895</v>
+      </c>
+      <c r="H191" t="s">
+        <v>26</v>
+      </c>
+      <c r="I191" t="s">
+        <v>31</v>
+      </c>
+      <c r="J191" t="s">
+        <v>68</v>
+      </c>
+      <c r="K191" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B192">
+        <v>2018</v>
+      </c>
+      <c r="C192" s="3">
+        <v>16</v>
+      </c>
+      <c r="D192" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192" t="s">
+        <v>896</v>
+      </c>
+      <c r="F192" t="s">
+        <v>897</v>
+      </c>
+      <c r="G192" t="s">
+        <v>898</v>
+      </c>
+      <c r="H192" t="s">
+        <v>26</v>
+      </c>
+      <c r="I192" t="s">
+        <v>31</v>
+      </c>
+      <c r="J192" t="s">
+        <v>81</v>
+      </c>
+      <c r="K192" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B193">
+        <v>2018</v>
+      </c>
+      <c r="C193" s="3">
+        <v>17</v>
+      </c>
+      <c r="D193" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193" t="s">
+        <v>899</v>
+      </c>
+      <c r="F193" t="s">
+        <v>900</v>
+      </c>
+      <c r="G193" t="s">
+        <v>901</v>
+      </c>
+      <c r="H193" t="s">
+        <v>57</v>
+      </c>
+      <c r="I193" t="s">
+        <v>31</v>
+      </c>
+      <c r="J193" t="s">
+        <v>170</v>
+      </c>
+      <c r="K193" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B194">
+        <v>2018</v>
+      </c>
+      <c r="C194" s="3">
+        <v>18</v>
+      </c>
+      <c r="D194" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194" t="s">
+        <v>903</v>
+      </c>
+      <c r="F194" t="s">
+        <v>904</v>
+      </c>
+      <c r="G194" t="s">
+        <v>905</v>
+      </c>
+      <c r="H194" t="s">
+        <v>57</v>
+      </c>
+      <c r="I194" t="s">
+        <v>31</v>
+      </c>
+      <c r="J194" t="s">
+        <v>58</v>
+      </c>
+      <c r="K194" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B195">
+        <v>2018</v>
+      </c>
+      <c r="C195" s="3">
+        <v>19</v>
+      </c>
+      <c r="D195" t="s">
+        <v>10</v>
+      </c>
+      <c r="E195" t="s">
+        <v>906</v>
+      </c>
+      <c r="F195" t="s">
+        <v>907</v>
+      </c>
+      <c r="G195" t="s">
+        <v>908</v>
+      </c>
+      <c r="H195" t="s">
+        <v>26</v>
+      </c>
+      <c r="I195" t="s">
+        <v>39</v>
+      </c>
+      <c r="J195" t="s">
+        <v>45</v>
+      </c>
+      <c r="K195" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B196">
+        <v>2018</v>
+      </c>
+      <c r="C196" s="3">
+        <v>20</v>
+      </c>
+      <c r="D196" t="s">
+        <v>10</v>
+      </c>
+      <c r="E196" t="s">
+        <v>909</v>
+      </c>
+      <c r="F196" t="s">
+        <v>910</v>
+      </c>
+      <c r="G196" t="s">
+        <v>911</v>
+      </c>
+      <c r="H196" t="s">
+        <v>21</v>
+      </c>
+      <c r="I196" t="s">
+        <v>39</v>
+      </c>
+      <c r="J196" t="s">
+        <v>912</v>
+      </c>
+      <c r="K196" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B197">
+        <v>2018</v>
+      </c>
+      <c r="C197" s="3">
+        <v>21</v>
+      </c>
+      <c r="D197" t="s">
+        <v>97</v>
+      </c>
+      <c r="E197" t="s">
+        <v>913</v>
+      </c>
+      <c r="F197" t="s">
+        <v>914</v>
+      </c>
+      <c r="G197" t="s">
+        <v>915</v>
+      </c>
+      <c r="H197" t="s">
+        <v>57</v>
+      </c>
+      <c r="I197" t="s">
+        <v>15</v>
+      </c>
+      <c r="J197" t="s">
+        <v>27</v>
+      </c>
+      <c r="K197" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B198">
+        <v>2018</v>
+      </c>
+      <c r="C198" s="3">
+        <v>22</v>
+      </c>
+      <c r="D198" t="s">
+        <v>97</v>
+      </c>
+      <c r="E198" t="s">
+        <v>917</v>
+      </c>
+      <c r="F198" t="s">
+        <v>918</v>
+      </c>
+      <c r="G198" t="s">
+        <v>919</v>
+      </c>
+      <c r="H198" t="s">
+        <v>26</v>
+      </c>
+      <c r="I198" t="s">
+        <v>31</v>
+      </c>
+      <c r="J198" t="s">
+        <v>32</v>
+      </c>
+      <c r="K198" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B199">
+        <v>2018</v>
+      </c>
+      <c r="C199" s="3">
+        <v>23</v>
+      </c>
+      <c r="D199" t="s">
+        <v>97</v>
+      </c>
+      <c r="E199" t="s">
+        <v>920</v>
+      </c>
+      <c r="F199" t="s">
+        <v>921</v>
+      </c>
+      <c r="G199" t="s">
+        <v>922</v>
+      </c>
+      <c r="H199" t="s">
+        <v>57</v>
+      </c>
+      <c r="I199" t="s">
+        <v>15</v>
+      </c>
+      <c r="J199" t="s">
+        <v>127</v>
+      </c>
+      <c r="K199" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B200">
+        <v>2018</v>
+      </c>
+      <c r="C200" s="3">
+        <v>24</v>
+      </c>
+      <c r="D200" t="s">
+        <v>97</v>
+      </c>
+      <c r="E200" t="s">
+        <v>923</v>
+      </c>
+      <c r="F200" t="s">
+        <v>924</v>
+      </c>
+      <c r="G200" t="s">
+        <v>925</v>
+      </c>
+      <c r="H200" t="s">
+        <v>26</v>
+      </c>
+      <c r="I200" t="s">
+        <v>39</v>
+      </c>
+      <c r="J200" t="s">
+        <v>72</v>
+      </c>
+      <c r="K200" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B201">
+        <v>2018</v>
+      </c>
+      <c r="C201" s="3">
+        <v>25</v>
+      </c>
+      <c r="D201" t="s">
+        <v>97</v>
+      </c>
+      <c r="E201" t="s">
+        <v>927</v>
+      </c>
+      <c r="F201" t="s">
+        <v>928</v>
+      </c>
+      <c r="G201" t="s">
+        <v>929</v>
+      </c>
+      <c r="H201" t="s">
+        <v>21</v>
+      </c>
+      <c r="I201" t="s">
+        <v>39</v>
+      </c>
+      <c r="J201" t="s">
+        <v>81</v>
+      </c>
+      <c r="K201" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B202">
+        <v>2018</v>
+      </c>
+      <c r="C202" s="3">
+        <v>26</v>
+      </c>
+      <c r="D202" t="s">
+        <v>97</v>
+      </c>
+      <c r="E202" t="s">
+        <v>931</v>
+      </c>
+      <c r="F202" t="s">
+        <v>932</v>
+      </c>
+      <c r="G202" t="s">
+        <v>933</v>
+      </c>
+      <c r="H202" t="s">
+        <v>57</v>
+      </c>
+      <c r="I202" t="s">
+        <v>31</v>
+      </c>
+      <c r="J202" t="s">
+        <v>40</v>
+      </c>
+      <c r="K202" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B203">
+        <v>2018</v>
+      </c>
+      <c r="C203" s="3">
+        <v>27</v>
+      </c>
+      <c r="D203" t="s">
+        <v>97</v>
+      </c>
+      <c r="E203" t="s">
+        <v>934</v>
+      </c>
+      <c r="F203" t="s">
+        <v>935</v>
+      </c>
+      <c r="G203" t="s">
+        <v>936</v>
+      </c>
+      <c r="H203" t="s">
+        <v>26</v>
+      </c>
+      <c r="I203" t="s">
+        <v>31</v>
+      </c>
+      <c r="J203" t="s">
+        <v>68</v>
+      </c>
+      <c r="K203" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B204">
+        <v>2018</v>
+      </c>
+      <c r="C204" s="3">
+        <v>28</v>
+      </c>
+      <c r="D204" t="s">
+        <v>97</v>
+      </c>
+      <c r="E204" t="s">
+        <v>937</v>
+      </c>
+      <c r="F204" t="s">
+        <v>938</v>
+      </c>
+      <c r="G204" t="s">
+        <v>939</v>
+      </c>
+      <c r="H204" t="s">
+        <v>26</v>
+      </c>
+      <c r="I204" t="s">
+        <v>39</v>
+      </c>
+      <c r="J204" t="s">
+        <v>170</v>
+      </c>
+      <c r="K204" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B205">
+        <v>2018</v>
+      </c>
+      <c r="C205" s="3">
+        <v>29</v>
+      </c>
+      <c r="D205" t="s">
+        <v>97</v>
+      </c>
+      <c r="E205" t="s">
+        <v>941</v>
+      </c>
+      <c r="F205" t="s">
+        <v>942</v>
+      </c>
+      <c r="G205" t="s">
+        <v>943</v>
+      </c>
+      <c r="H205" t="s">
+        <v>57</v>
+      </c>
+      <c r="I205" t="s">
+        <v>31</v>
+      </c>
+      <c r="J205" t="s">
+        <v>483</v>
+      </c>
+      <c r="K205" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B206">
+        <v>2018</v>
+      </c>
+      <c r="C206" s="3">
+        <v>30</v>
+      </c>
+      <c r="D206" t="s">
+        <v>97</v>
+      </c>
+      <c r="E206" t="s">
+        <v>944</v>
+      </c>
+      <c r="F206" t="s">
+        <v>945</v>
+      </c>
+      <c r="G206" t="s">
+        <v>946</v>
+      </c>
+      <c r="H206" t="s">
+        <v>26</v>
+      </c>
+      <c r="I206" t="s">
+        <v>39</v>
+      </c>
+      <c r="J206" t="s">
+        <v>45</v>
+      </c>
+      <c r="K206" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B207">
+        <v>2018</v>
+      </c>
+      <c r="C207" s="3">
+        <v>31</v>
+      </c>
+      <c r="D207" t="s">
+        <v>97</v>
+      </c>
+      <c r="E207" t="s">
+        <v>947</v>
+      </c>
+      <c r="F207" t="s">
+        <v>948</v>
+      </c>
+      <c r="G207" t="s">
+        <v>949</v>
+      </c>
+      <c r="H207" t="s">
+        <v>57</v>
+      </c>
+      <c r="I207" t="s">
+        <v>39</v>
+      </c>
+      <c r="J207" t="s">
+        <v>72</v>
+      </c>
+      <c r="K207" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B208">
+        <v>2018</v>
+      </c>
+      <c r="C208" s="3">
+        <v>32</v>
+      </c>
+      <c r="D208" t="s">
+        <v>97</v>
+      </c>
+      <c r="E208" t="s">
+        <v>951</v>
+      </c>
+      <c r="F208" t="s">
+        <v>952</v>
+      </c>
+      <c r="G208" t="s">
+        <v>953</v>
+      </c>
+      <c r="H208" t="s">
+        <v>26</v>
+      </c>
+      <c r="I208" t="s">
+        <v>31</v>
+      </c>
+      <c r="J208" t="s">
+        <v>233</v>
+      </c>
+      <c r="K208" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B209">
+        <v>2017</v>
+      </c>
+      <c r="C209" s="3">
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
+        <v>10</v>
+      </c>
+      <c r="E209" t="s">
+        <v>664</v>
+      </c>
+      <c r="F209" t="s">
+        <v>665</v>
+      </c>
+      <c r="G209" t="s">
+        <v>666</v>
+      </c>
+      <c r="H209" t="s">
+        <v>14</v>
+      </c>
+      <c r="I209" t="s">
+        <v>15</v>
+      </c>
+      <c r="J209" t="s">
+        <v>16</v>
+      </c>
+      <c r="K209" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B210">
+        <v>2017</v>
+      </c>
+      <c r="C210" s="3">
+        <v>2</v>
+      </c>
+      <c r="D210" t="s">
+        <v>10</v>
+      </c>
+      <c r="E210" t="s">
+        <v>667</v>
+      </c>
+      <c r="F210" t="s">
+        <v>668</v>
+      </c>
+      <c r="G210" t="s">
+        <v>669</v>
+      </c>
+      <c r="H210" t="s">
+        <v>21</v>
+      </c>
+      <c r="I210" t="s">
+        <v>15</v>
+      </c>
+      <c r="J210" t="s">
+        <v>22</v>
+      </c>
+      <c r="K210" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B211">
+        <v>2017</v>
+      </c>
+      <c r="C211" s="3">
+        <v>3</v>
+      </c>
+      <c r="D211" t="s">
+        <v>10</v>
+      </c>
+      <c r="E211" t="s">
+        <v>670</v>
+      </c>
+      <c r="F211" t="s">
+        <v>671</v>
+      </c>
+      <c r="G211" t="s">
+        <v>672</v>
+      </c>
+      <c r="H211" t="s">
+        <v>57</v>
+      </c>
+      <c r="I211" t="s">
+        <v>31</v>
+      </c>
+      <c r="J211" t="s">
+        <v>92</v>
+      </c>
+      <c r="K211" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B212">
+        <v>2017</v>
+      </c>
+      <c r="C212" s="3">
+        <v>4</v>
+      </c>
+      <c r="D212" t="s">
+        <v>10</v>
+      </c>
+      <c r="E212" t="s">
+        <v>673</v>
+      </c>
+      <c r="F212" t="s">
+        <v>674</v>
+      </c>
+      <c r="G212" t="s">
+        <v>675</v>
+      </c>
+      <c r="H212" t="s">
+        <v>26</v>
+      </c>
+      <c r="I212" t="s">
+        <v>15</v>
+      </c>
+      <c r="J212" t="s">
+        <v>49</v>
+      </c>
+      <c r="K212" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B213">
+        <v>2017</v>
+      </c>
+      <c r="C213" s="3">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>10</v>
+      </c>
+      <c r="E213" t="s">
+        <v>676</v>
+      </c>
+      <c r="F213" t="s">
+        <v>677</v>
+      </c>
+      <c r="G213" t="s">
+        <v>678</v>
+      </c>
+      <c r="H213" t="s">
+        <v>21</v>
+      </c>
+      <c r="I213" t="s">
+        <v>39</v>
+      </c>
+      <c r="J213" t="s">
+        <v>45</v>
+      </c>
+      <c r="K213" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B214">
+        <v>2017</v>
+      </c>
+      <c r="C214" s="3">
+        <v>6</v>
+      </c>
+      <c r="D214" t="s">
+        <v>10</v>
+      </c>
+      <c r="E214" t="s">
+        <v>679</v>
+      </c>
+      <c r="F214" t="s">
+        <v>680</v>
+      </c>
+      <c r="G214" t="s">
+        <v>681</v>
+      </c>
+      <c r="H214" t="s">
+        <v>26</v>
+      </c>
+      <c r="I214" t="s">
+        <v>15</v>
+      </c>
+      <c r="J214" t="s">
+        <v>27</v>
+      </c>
+      <c r="K214" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B215">
+        <v>2017</v>
+      </c>
+      <c r="C215" s="3">
+        <v>7</v>
+      </c>
+      <c r="D215" t="s">
+        <v>10</v>
+      </c>
+      <c r="E215" t="s">
+        <v>682</v>
+      </c>
+      <c r="F215" t="s">
+        <v>683</v>
+      </c>
+      <c r="G215" t="s">
+        <v>684</v>
+      </c>
+      <c r="H215" t="s">
+        <v>57</v>
+      </c>
+      <c r="I215" t="s">
+        <v>15</v>
+      </c>
+      <c r="J215" t="s">
+        <v>685</v>
+      </c>
+      <c r="K215" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B216">
+        <v>2017</v>
+      </c>
+      <c r="C216" s="3">
+        <v>8</v>
+      </c>
+      <c r="D216" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" t="s">
+        <v>686</v>
+      </c>
+      <c r="F216" t="s">
+        <v>687</v>
+      </c>
+      <c r="G216" t="s">
+        <v>688</v>
+      </c>
+      <c r="H216" t="s">
+        <v>21</v>
+      </c>
+      <c r="I216" t="s">
+        <v>39</v>
+      </c>
+      <c r="J216" t="s">
+        <v>81</v>
+      </c>
+      <c r="K216" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B217">
+        <v>2017</v>
+      </c>
+      <c r="C217" s="3">
+        <v>9</v>
+      </c>
+      <c r="D217" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217" t="s">
+        <v>689</v>
+      </c>
+      <c r="F217" t="s">
+        <v>690</v>
+      </c>
+      <c r="G217" t="s">
+        <v>691</v>
+      </c>
+      <c r="H217" t="s">
+        <v>26</v>
+      </c>
+      <c r="I217" t="s">
+        <v>39</v>
+      </c>
+      <c r="J217" t="s">
+        <v>72</v>
+      </c>
+      <c r="K217" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B218">
+        <v>2017</v>
+      </c>
+      <c r="C218" s="3">
+        <v>10</v>
+      </c>
+      <c r="D218" t="s">
+        <v>10</v>
+      </c>
+      <c r="E218" t="s">
+        <v>692</v>
+      </c>
+      <c r="F218" t="s">
+        <v>693</v>
+      </c>
+      <c r="G218" t="s">
+        <v>694</v>
+      </c>
+      <c r="H218" t="s">
+        <v>21</v>
+      </c>
+      <c r="I218" t="s">
+        <v>31</v>
+      </c>
+      <c r="J218" t="s">
+        <v>53</v>
+      </c>
+      <c r="K218" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B219">
+        <v>2017</v>
+      </c>
+      <c r="C219" s="3">
+        <v>11</v>
+      </c>
+      <c r="D219" t="s">
+        <v>10</v>
+      </c>
+      <c r="E219" t="s">
+        <v>695</v>
+      </c>
+      <c r="F219" t="s">
+        <v>696</v>
+      </c>
+      <c r="G219" t="s">
+        <v>697</v>
+      </c>
+      <c r="H219" t="s">
+        <v>21</v>
+      </c>
+      <c r="I219" t="s">
+        <v>31</v>
+      </c>
+      <c r="J219" t="s">
+        <v>32</v>
+      </c>
+      <c r="K219" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B220">
+        <v>2017</v>
+      </c>
+      <c r="C220" s="3">
+        <v>12</v>
+      </c>
+      <c r="D220" t="s">
+        <v>10</v>
+      </c>
+      <c r="E220" t="s">
+        <v>698</v>
+      </c>
+      <c r="F220" t="s">
+        <v>699</v>
+      </c>
+      <c r="G220" t="s">
+        <v>700</v>
+      </c>
+      <c r="H220" t="s">
+        <v>21</v>
+      </c>
+      <c r="I220" t="s">
+        <v>15</v>
+      </c>
+      <c r="J220" t="s">
+        <v>22</v>
+      </c>
+      <c r="K220" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B221">
+        <v>2017</v>
+      </c>
+      <c r="C221" s="3">
+        <v>13</v>
+      </c>
+      <c r="D221" t="s">
+        <v>10</v>
+      </c>
+      <c r="E221" t="s">
+        <v>701</v>
+      </c>
+      <c r="F221" t="s">
+        <v>702</v>
+      </c>
+      <c r="G221" t="s">
+        <v>703</v>
+      </c>
+      <c r="H221" t="s">
+        <v>26</v>
+      </c>
+      <c r="I221" t="s">
+        <v>31</v>
+      </c>
+      <c r="J221" t="s">
+        <v>704</v>
+      </c>
+      <c r="K221" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B222">
+        <v>2017</v>
+      </c>
+      <c r="C222" s="3">
+        <v>14</v>
+      </c>
+      <c r="D222" t="s">
+        <v>10</v>
+      </c>
+      <c r="E222" t="s">
+        <v>705</v>
+      </c>
+      <c r="F222" t="s">
+        <v>706</v>
+      </c>
+      <c r="G222" t="s">
+        <v>707</v>
+      </c>
+      <c r="H222" t="s">
+        <v>57</v>
+      </c>
+      <c r="I222" t="s">
+        <v>31</v>
+      </c>
+      <c r="J222" t="s">
+        <v>545</v>
+      </c>
+      <c r="K222" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B223">
+        <v>2017</v>
+      </c>
+      <c r="C223" s="3">
+        <v>15</v>
+      </c>
+      <c r="D223" t="s">
+        <v>10</v>
+      </c>
+      <c r="E223" t="s">
+        <v>709</v>
+      </c>
+      <c r="F223" t="s">
+        <v>710</v>
+      </c>
+      <c r="G223" t="s">
+        <v>711</v>
+      </c>
+      <c r="H223" t="s">
+        <v>26</v>
+      </c>
+      <c r="I223" t="s">
+        <v>39</v>
+      </c>
+      <c r="J223" t="s">
+        <v>40</v>
+      </c>
+      <c r="K223" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B224">
+        <v>2017</v>
+      </c>
+      <c r="C224" s="3">
+        <v>16</v>
+      </c>
+      <c r="D224" t="s">
+        <v>10</v>
+      </c>
+      <c r="E224" t="s">
+        <v>712</v>
+      </c>
+      <c r="F224" t="s">
+        <v>713</v>
+      </c>
+      <c r="G224" t="s">
+        <v>714</v>
+      </c>
+      <c r="H224" t="s">
+        <v>57</v>
+      </c>
+      <c r="I224" t="s">
+        <v>39</v>
+      </c>
+      <c r="J224" t="s">
+        <v>45</v>
+      </c>
+      <c r="K224" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B225">
+        <v>2017</v>
+      </c>
+      <c r="C225" s="3">
+        <v>17</v>
+      </c>
+      <c r="D225" t="s">
+        <v>10</v>
+      </c>
+      <c r="E225" t="s">
+        <v>715</v>
+      </c>
+      <c r="F225" t="s">
+        <v>716</v>
+      </c>
+      <c r="G225" t="s">
+        <v>717</v>
+      </c>
+      <c r="H225" t="s">
+        <v>14</v>
+      </c>
+      <c r="I225" t="s">
+        <v>31</v>
+      </c>
+      <c r="J225" t="s">
+        <v>49</v>
+      </c>
+      <c r="K225" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B226">
+        <v>2017</v>
+      </c>
+      <c r="C226" s="3">
+        <v>18</v>
+      </c>
+      <c r="D226" t="s">
+        <v>10</v>
+      </c>
+      <c r="E226" t="s">
+        <v>718</v>
+      </c>
+      <c r="F226" t="s">
+        <v>719</v>
+      </c>
+      <c r="G226" t="s">
+        <v>720</v>
+      </c>
+      <c r="H226" t="s">
+        <v>57</v>
+      </c>
+      <c r="I226" t="s">
+        <v>31</v>
+      </c>
+      <c r="J226" t="s">
+        <v>721</v>
+      </c>
+      <c r="K226" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="227" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B227">
+        <v>2017</v>
+      </c>
+      <c r="C227" s="3">
+        <v>19</v>
+      </c>
+      <c r="D227" t="s">
+        <v>10</v>
+      </c>
+      <c r="E227" t="s">
+        <v>722</v>
+      </c>
+      <c r="F227" t="s">
+        <v>723</v>
+      </c>
+      <c r="G227" t="s">
+        <v>724</v>
+      </c>
+      <c r="H227" t="s">
+        <v>14</v>
+      </c>
+      <c r="I227" t="s">
+        <v>31</v>
+      </c>
+      <c r="J227" t="s">
+        <v>233</v>
+      </c>
+      <c r="K227" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="228" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B228">
+        <v>2017</v>
+      </c>
+      <c r="C228" s="3">
+        <v>20</v>
+      </c>
+      <c r="D228" t="s">
+        <v>10</v>
+      </c>
+      <c r="E228" t="s">
+        <v>726</v>
+      </c>
+      <c r="F228" t="s">
+        <v>727</v>
+      </c>
+      <c r="G228" t="s">
+        <v>728</v>
+      </c>
+      <c r="H228" t="s">
+        <v>21</v>
+      </c>
+      <c r="I228" t="s">
+        <v>15</v>
+      </c>
+      <c r="J228" t="s">
+        <v>729</v>
+      </c>
+      <c r="K228" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B229">
+        <v>2017</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D229" t="s">
+        <v>97</v>
+      </c>
+      <c r="E229" t="s">
+        <v>730</v>
+      </c>
+      <c r="F229" t="s">
+        <v>731</v>
+      </c>
+      <c r="G229" t="s">
+        <v>732</v>
+      </c>
+      <c r="H229" t="s">
+        <v>57</v>
+      </c>
+      <c r="I229" t="s">
+        <v>15</v>
+      </c>
+      <c r="J229" t="s">
+        <v>127</v>
+      </c>
+      <c r="K229" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="230" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B230">
+        <v>2017</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D230" t="s">
+        <v>97</v>
+      </c>
+      <c r="E230" t="s">
+        <v>734</v>
+      </c>
+      <c r="F230" t="s">
+        <v>735</v>
+      </c>
+      <c r="G230" t="s">
+        <v>736</v>
+      </c>
+      <c r="H230" t="s">
+        <v>57</v>
+      </c>
+      <c r="I230" t="s">
+        <v>15</v>
+      </c>
+      <c r="J230" t="s">
+        <v>127</v>
+      </c>
+      <c r="K230" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B231">
+        <v>2017</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D231" t="s">
+        <v>97</v>
+      </c>
+      <c r="E231" t="s">
+        <v>737</v>
+      </c>
+      <c r="F231" t="s">
+        <v>738</v>
+      </c>
+      <c r="G231" t="s">
+        <v>739</v>
+      </c>
+      <c r="H231" t="s">
+        <v>57</v>
+      </c>
+      <c r="I231" t="s">
+        <v>15</v>
+      </c>
+      <c r="J231" t="s">
+        <v>27</v>
+      </c>
+      <c r="K231" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="232" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B232">
+        <v>2017</v>
+      </c>
+      <c r="C232" s="3">
+        <v>25</v>
+      </c>
+      <c r="D232" t="s">
+        <v>97</v>
+      </c>
+      <c r="E232" t="s">
+        <v>741</v>
+      </c>
+      <c r="F232" t="s">
+        <v>742</v>
+      </c>
+      <c r="G232" t="s">
+        <v>743</v>
+      </c>
+      <c r="H232" t="s">
+        <v>26</v>
+      </c>
+      <c r="I232" t="s">
+        <v>39</v>
+      </c>
+      <c r="J232" t="s">
+        <v>609</v>
+      </c>
+      <c r="K232" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B233">
+        <v>2017</v>
+      </c>
+      <c r="C233" s="3">
+        <v>30</v>
+      </c>
+      <c r="D233" t="s">
+        <v>97</v>
+      </c>
+      <c r="E233" t="s">
+        <v>744</v>
+      </c>
+      <c r="F233" t="s">
+        <v>745</v>
+      </c>
+      <c r="G233" t="s">
+        <v>746</v>
+      </c>
+      <c r="H233" t="s">
+        <v>26</v>
+      </c>
+      <c r="I233" t="s">
+        <v>39</v>
+      </c>
+      <c r="J233" t="s">
+        <v>454</v>
+      </c>
+      <c r="K233" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="234" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B234">
+        <v>2017</v>
+      </c>
+      <c r="C234" s="3">
+        <v>32</v>
+      </c>
+      <c r="D234" t="s">
+        <v>97</v>
+      </c>
+      <c r="E234" t="s">
+        <v>748</v>
+      </c>
+      <c r="F234" t="s">
+        <v>749</v>
+      </c>
+      <c r="G234" t="s">
+        <v>750</v>
+      </c>
+      <c r="H234" t="s">
+        <v>57</v>
+      </c>
+      <c r="I234" t="s">
+        <v>31</v>
+      </c>
+      <c r="J234" t="s">
+        <v>233</v>
+      </c>
+      <c r="K234" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="235" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B235">
+        <v>2015</v>
+      </c>
+      <c r="C235" s="3">
+        <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>10</v>
+      </c>
+      <c r="E235" t="s">
+        <v>752</v>
+      </c>
+      <c r="F235" t="s">
+        <v>753</v>
+      </c>
+      <c r="G235" t="s">
+        <v>754</v>
+      </c>
+      <c r="H235" t="s">
+        <v>14</v>
+      </c>
+      <c r="I235" t="s">
+        <v>15</v>
+      </c>
+      <c r="J235" t="s">
+        <v>16</v>
+      </c>
+      <c r="K235" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B236">
+        <v>2015</v>
+      </c>
+      <c r="C236" s="3">
+        <v>2</v>
+      </c>
+      <c r="D236" t="s">
+        <v>10</v>
+      </c>
+      <c r="E236" t="s">
+        <v>755</v>
+      </c>
+      <c r="F236" t="s">
+        <v>756</v>
+      </c>
+      <c r="G236" t="s">
+        <v>757</v>
+      </c>
+      <c r="H236" t="s">
+        <v>14</v>
+      </c>
+      <c r="I236" t="s">
+        <v>15</v>
+      </c>
+      <c r="J236" t="s">
+        <v>22</v>
+      </c>
+      <c r="K236" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B237">
+        <v>2015</v>
+      </c>
+      <c r="C237" s="3">
+        <v>3</v>
+      </c>
+      <c r="D237" t="s">
+        <v>10</v>
+      </c>
+      <c r="E237" t="s">
+        <v>758</v>
+      </c>
+      <c r="F237" t="s">
+        <v>759</v>
+      </c>
+      <c r="G237" t="s">
+        <v>760</v>
+      </c>
+      <c r="H237" t="s">
+        <v>57</v>
+      </c>
+      <c r="I237" t="s">
+        <v>39</v>
+      </c>
+      <c r="J237" t="s">
+        <v>45</v>
+      </c>
+      <c r="K237" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="238" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B238">
+        <v>2015</v>
+      </c>
+      <c r="C238" s="3">
+        <v>4</v>
+      </c>
+      <c r="D238" t="s">
+        <v>10</v>
+      </c>
+      <c r="E238" t="s">
+        <v>761</v>
+      </c>
+      <c r="F238" t="s">
+        <v>762</v>
+      </c>
+      <c r="G238" t="s">
+        <v>763</v>
+      </c>
+      <c r="H238" t="s">
+        <v>26</v>
+      </c>
+      <c r="I238" t="s">
+        <v>15</v>
+      </c>
+      <c r="J238" t="s">
+        <v>27</v>
+      </c>
+      <c r="K238" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B239">
+        <v>2015</v>
+      </c>
+      <c r="C239" s="3">
+        <v>5</v>
+      </c>
+      <c r="D239" t="s">
+        <v>10</v>
+      </c>
+      <c r="E239" t="s">
+        <v>764</v>
+      </c>
+      <c r="F239" t="s">
+        <v>765</v>
+      </c>
+      <c r="G239" t="s">
+        <v>766</v>
+      </c>
+      <c r="H239" t="s">
+        <v>21</v>
+      </c>
+      <c r="I239" t="s">
+        <v>39</v>
+      </c>
+      <c r="J239" t="s">
+        <v>96</v>
+      </c>
+      <c r="K239" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="240" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B240">
+        <v>2015</v>
+      </c>
+      <c r="C240" s="3">
+        <v>6</v>
+      </c>
+      <c r="D240" t="s">
+        <v>10</v>
+      </c>
+      <c r="E240" t="s">
+        <v>768</v>
+      </c>
+      <c r="F240" t="s">
+        <v>769</v>
+      </c>
+      <c r="G240" t="s">
+        <v>770</v>
+      </c>
+      <c r="H240" t="s">
+        <v>21</v>
+      </c>
+      <c r="I240" t="s">
+        <v>15</v>
+      </c>
+      <c r="J240" t="s">
+        <v>49</v>
+      </c>
+      <c r="K240" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="241" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B241">
+        <v>2015</v>
+      </c>
+      <c r="C241" s="3">
+        <v>7</v>
+      </c>
+      <c r="D241" t="s">
+        <v>10</v>
+      </c>
+      <c r="E241" t="s">
+        <v>771</v>
+      </c>
+      <c r="F241" t="s">
+        <v>772</v>
+      </c>
+      <c r="G241" t="s">
+        <v>773</v>
+      </c>
+      <c r="H241" t="s">
+        <v>26</v>
+      </c>
+      <c r="I241" t="s">
+        <v>31</v>
+      </c>
+      <c r="J241" t="s">
+        <v>32</v>
+      </c>
+      <c r="K241" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B242">
+        <v>2015</v>
+      </c>
+      <c r="C242" s="3">
+        <v>8</v>
+      </c>
+      <c r="D242" t="s">
+        <v>10</v>
+      </c>
+      <c r="E242" t="s">
+        <v>774</v>
+      </c>
+      <c r="F242" t="s">
+        <v>775</v>
+      </c>
+      <c r="G242" t="s">
+        <v>776</v>
+      </c>
+      <c r="H242" t="s">
+        <v>21</v>
+      </c>
+      <c r="I242" t="s">
+        <v>31</v>
+      </c>
+      <c r="J242" t="s">
+        <v>53</v>
+      </c>
+      <c r="K242" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="243" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B243">
+        <v>2015</v>
+      </c>
+      <c r="C243" s="3">
+        <v>9</v>
+      </c>
+      <c r="D243" t="s">
+        <v>10</v>
+      </c>
+      <c r="E243" t="s">
+        <v>777</v>
+      </c>
+      <c r="F243" t="s">
+        <v>778</v>
+      </c>
+      <c r="G243" t="s">
+        <v>779</v>
+      </c>
+      <c r="H243" t="s">
+        <v>21</v>
+      </c>
+      <c r="I243" t="s">
+        <v>31</v>
+      </c>
+      <c r="J243" t="s">
+        <v>170</v>
+      </c>
+      <c r="K243" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="244" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B244">
+        <v>2015</v>
+      </c>
+      <c r="C244" s="3">
+        <v>10</v>
+      </c>
+      <c r="D244" t="s">
+        <v>10</v>
+      </c>
+      <c r="E244" t="s">
+        <v>781</v>
+      </c>
+      <c r="F244" t="s">
+        <v>782</v>
+      </c>
+      <c r="G244" t="s">
+        <v>783</v>
+      </c>
+      <c r="H244" t="s">
+        <v>21</v>
+      </c>
+      <c r="I244" t="s">
+        <v>39</v>
+      </c>
+      <c r="J244" t="s">
+        <v>81</v>
+      </c>
+      <c r="K244" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B245">
+        <v>2015</v>
+      </c>
+      <c r="C245" s="3">
+        <v>11</v>
+      </c>
+      <c r="D245" t="s">
+        <v>10</v>
+      </c>
+      <c r="E245" t="s">
+        <v>784</v>
+      </c>
+      <c r="F245" t="s">
+        <v>785</v>
+      </c>
+      <c r="G245" t="s">
+        <v>786</v>
+      </c>
+      <c r="H245" t="s">
+        <v>57</v>
+      </c>
+      <c r="I245" t="s">
+        <v>31</v>
+      </c>
+      <c r="J245" t="s">
+        <v>32</v>
+      </c>
+      <c r="K245" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="246" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B246">
+        <v>2015</v>
+      </c>
+      <c r="C246" s="3">
+        <v>12</v>
+      </c>
+      <c r="D246" t="s">
+        <v>10</v>
+      </c>
+      <c r="E246" t="s">
+        <v>787</v>
+      </c>
+      <c r="F246" t="s">
+        <v>788</v>
+      </c>
+      <c r="G246" t="s">
+        <v>789</v>
+      </c>
+      <c r="H246" t="s">
+        <v>21</v>
+      </c>
+      <c r="I246" t="s">
+        <v>39</v>
+      </c>
+      <c r="J246" t="s">
+        <v>72</v>
+      </c>
+      <c r="K246" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B247">
+        <v>2015</v>
+      </c>
+      <c r="C247" s="3">
+        <v>13</v>
+      </c>
+      <c r="D247" t="s">
+        <v>10</v>
+      </c>
+      <c r="E247" t="s">
+        <v>790</v>
+      </c>
+      <c r="F247" t="s">
+        <v>791</v>
+      </c>
+      <c r="G247" t="s">
+        <v>792</v>
+      </c>
+      <c r="H247" t="s">
+        <v>26</v>
+      </c>
+      <c r="I247" t="s">
+        <v>39</v>
+      </c>
+      <c r="J247" t="s">
+        <v>45</v>
+      </c>
+      <c r="K247" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="248" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B248">
+        <v>2015</v>
+      </c>
+      <c r="C248" s="3">
+        <v>14</v>
+      </c>
+      <c r="D248" t="s">
+        <v>10</v>
+      </c>
+      <c r="E248" t="s">
+        <v>793</v>
+      </c>
+      <c r="F248" t="s">
+        <v>794</v>
+      </c>
+      <c r="G248" t="s">
+        <v>795</v>
+      </c>
+      <c r="H248" t="s">
+        <v>57</v>
+      </c>
+      <c r="I248" t="s">
+        <v>15</v>
+      </c>
+      <c r="J248" t="s">
+        <v>127</v>
+      </c>
+      <c r="K248" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="249" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B249">
+        <v>2015</v>
+      </c>
+      <c r="C249" s="3">
+        <v>15</v>
+      </c>
+      <c r="D249" t="s">
+        <v>10</v>
+      </c>
+      <c r="E249" t="s">
+        <v>796</v>
+      </c>
+      <c r="F249" t="s">
+        <v>797</v>
+      </c>
+      <c r="G249" t="s">
+        <v>798</v>
+      </c>
+      <c r="H249" t="s">
+        <v>57</v>
+      </c>
+      <c r="I249" t="s">
+        <v>31</v>
+      </c>
+      <c r="J249" t="s">
+        <v>170</v>
+      </c>
+      <c r="K249" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="250" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B250">
+        <v>2015</v>
+      </c>
+      <c r="C250" s="3">
+        <v>16</v>
+      </c>
+      <c r="D250" t="s">
+        <v>10</v>
+      </c>
+      <c r="E250" t="s">
+        <v>800</v>
+      </c>
+      <c r="F250" t="s">
+        <v>801</v>
+      </c>
+      <c r="G250" t="s">
+        <v>802</v>
+      </c>
+      <c r="H250" t="s">
+        <v>21</v>
+      </c>
+      <c r="I250" t="s">
+        <v>15</v>
+      </c>
+      <c r="J250" t="s">
+        <v>49</v>
+      </c>
+      <c r="K250" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="251" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B251">
+        <v>2015</v>
+      </c>
+      <c r="C251" s="3">
+        <v>17</v>
+      </c>
+      <c r="D251" t="s">
+        <v>10</v>
+      </c>
+      <c r="E251" t="s">
+        <v>804</v>
+      </c>
+      <c r="F251" t="s">
+        <v>805</v>
+      </c>
+      <c r="G251" t="s">
+        <v>806</v>
+      </c>
+      <c r="H251" t="s">
+        <v>26</v>
+      </c>
+      <c r="I251" t="s">
+        <v>31</v>
+      </c>
+      <c r="J251" t="s">
+        <v>68</v>
+      </c>
+      <c r="K251" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="252" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B252">
+        <v>2015</v>
+      </c>
+      <c r="C252" s="3">
+        <v>18</v>
+      </c>
+      <c r="D252" t="s">
+        <v>10</v>
+      </c>
+      <c r="E252" t="s">
+        <v>807</v>
+      </c>
+      <c r="F252" t="s">
+        <v>808</v>
+      </c>
+      <c r="G252" t="s">
+        <v>809</v>
+      </c>
+      <c r="H252" t="s">
+        <v>57</v>
+      </c>
+      <c r="I252" t="s">
+        <v>31</v>
+      </c>
+      <c r="J252" t="s">
+        <v>645</v>
+      </c>
+      <c r="K252" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="253" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B253">
+        <v>2015</v>
+      </c>
+      <c r="C253" s="3">
+        <v>19</v>
+      </c>
+      <c r="D253" t="s">
+        <v>10</v>
+      </c>
+      <c r="E253" t="s">
+        <v>810</v>
+      </c>
+      <c r="F253" t="s">
+        <v>811</v>
+      </c>
+      <c r="G253" t="s">
+        <v>812</v>
+      </c>
+      <c r="H253" t="s">
+        <v>26</v>
+      </c>
+      <c r="I253" t="s">
+        <v>31</v>
+      </c>
+      <c r="J253" t="s">
+        <v>32</v>
+      </c>
+      <c r="K253" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="254" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B254">
+        <v>2015</v>
+      </c>
+      <c r="C254" s="3">
+        <v>20</v>
+      </c>
+      <c r="D254" t="s">
+        <v>10</v>
+      </c>
+      <c r="E254" t="s">
+        <v>813</v>
+      </c>
+      <c r="F254" t="s">
+        <v>814</v>
+      </c>
+      <c r="G254" t="s">
+        <v>815</v>
+      </c>
+      <c r="H254" t="s">
+        <v>14</v>
+      </c>
+      <c r="I254" t="s">
+        <v>15</v>
+      </c>
+      <c r="J254" t="s">
+        <v>16</v>
+      </c>
+      <c r="K254" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="255" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B255">
+        <v>2015</v>
+      </c>
+      <c r="C255" s="3">
+        <v>21</v>
+      </c>
+      <c r="D255" t="s">
+        <v>97</v>
+      </c>
+      <c r="E255" t="s">
+        <v>816</v>
+      </c>
+      <c r="F255" t="s">
+        <v>817</v>
+      </c>
+      <c r="G255" t="s">
+        <v>818</v>
+      </c>
+      <c r="H255" t="s">
+        <v>26</v>
+      </c>
+      <c r="I255" t="s">
+        <v>15</v>
+      </c>
+      <c r="J255" t="s">
+        <v>27</v>
+      </c>
+      <c r="K255" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="256" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B256">
+        <v>2015</v>
+      </c>
+      <c r="C256" s="3">
+        <v>22</v>
+      </c>
+      <c r="D256" t="s">
+        <v>97</v>
+      </c>
+      <c r="E256" t="s">
+        <v>820</v>
+      </c>
+      <c r="F256" t="s">
+        <v>821</v>
+      </c>
+      <c r="G256" t="s">
+        <v>822</v>
+      </c>
+      <c r="H256" t="s">
+        <v>26</v>
+      </c>
+      <c r="I256" t="s">
+        <v>15</v>
+      </c>
+      <c r="J256" t="s">
+        <v>16</v>
+      </c>
+      <c r="K256" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="257" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B257">
+        <v>2015</v>
+      </c>
+      <c r="C257" s="3">
+        <v>23</v>
+      </c>
+      <c r="D257" t="s">
+        <v>97</v>
+      </c>
+      <c r="E257" t="s">
+        <v>823</v>
+      </c>
+      <c r="F257" t="s">
+        <v>824</v>
+      </c>
+      <c r="G257" t="s">
+        <v>825</v>
+      </c>
+      <c r="H257" t="s">
+        <v>26</v>
+      </c>
+      <c r="I257" t="s">
+        <v>31</v>
+      </c>
+      <c r="J257" t="s">
+        <v>81</v>
+      </c>
+      <c r="K257" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="258" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B258">
+        <v>2015</v>
+      </c>
+      <c r="C258" s="3">
+        <v>24</v>
+      </c>
+      <c r="D258" t="s">
+        <v>97</v>
+      </c>
+      <c r="E258" t="s">
+        <v>827</v>
+      </c>
+      <c r="F258" t="s">
+        <v>828</v>
+      </c>
+      <c r="G258" t="s">
+        <v>829</v>
+      </c>
+      <c r="H258" t="s">
+        <v>26</v>
+      </c>
+      <c r="I258" t="s">
+        <v>39</v>
+      </c>
+      <c r="J258" t="s">
+        <v>72</v>
+      </c>
+      <c r="K258" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="259" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B259">
+        <v>2015</v>
+      </c>
+      <c r="C259" s="3">
+        <v>26</v>
+      </c>
+      <c r="D259" t="s">
+        <v>97</v>
+      </c>
+      <c r="E259" t="s">
+        <v>831</v>
+      </c>
+      <c r="F259" t="s">
+        <v>832</v>
+      </c>
+      <c r="G259" t="s">
+        <v>833</v>
+      </c>
+      <c r="H259" t="s">
+        <v>21</v>
+      </c>
+      <c r="I259" t="s">
+        <v>31</v>
+      </c>
+      <c r="J259" t="s">
+        <v>170</v>
+      </c>
+      <c r="K259" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="260" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B260">
+        <v>2015</v>
+      </c>
+      <c r="C260" s="3">
+        <v>29</v>
+      </c>
+      <c r="D260" t="s">
+        <v>97</v>
+      </c>
+      <c r="E260" t="s">
+        <v>835</v>
+      </c>
+      <c r="F260" t="s">
+        <v>836</v>
+      </c>
+      <c r="G260" t="s">
+        <v>837</v>
+      </c>
+      <c r="H260" t="s">
+        <v>26</v>
+      </c>
+      <c r="I260" t="s">
+        <v>39</v>
+      </c>
+      <c r="J260" t="s">
+        <v>838</v>
+      </c>
+      <c r="K260" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="261" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B261">
+        <v>2015</v>
+      </c>
+      <c r="C261" s="3">
+        <v>31</v>
+      </c>
+      <c r="D261" t="s">
+        <v>97</v>
+      </c>
+      <c r="E261" t="s">
+        <v>840</v>
+      </c>
+      <c r="F261" t="s">
+        <v>841</v>
+      </c>
+      <c r="G261" t="s">
+        <v>842</v>
+      </c>
+      <c r="H261" t="s">
+        <v>57</v>
+      </c>
+      <c r="I261" t="s">
+        <v>39</v>
+      </c>
+      <c r="J261" t="s">
+        <v>45</v>
+      </c>
+      <c r="K261" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="262" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B262">
+        <v>2015</v>
+      </c>
+      <c r="C262" s="3">
+        <v>32</v>
+      </c>
+      <c r="D262" t="s">
+        <v>97</v>
+      </c>
+      <c r="E262" t="s">
+        <v>843</v>
+      </c>
+      <c r="F262" t="s">
+        <v>844</v>
+      </c>
+      <c r="G262" t="s">
+        <v>845</v>
+      </c>
+      <c r="H262" t="s">
+        <v>57</v>
+      </c>
+      <c r="I262" t="s">
+        <v>31</v>
+      </c>
+      <c r="J262" t="s">
+        <v>846</v>
+      </c>
+      <c r="K262" t="s">
+        <v>847</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
